--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_10/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_10/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999999967758</v>
+        <v>36.46761472783696</v>
       </c>
       <c r="B2" t="n">
-        <v>90.18500985662632</v>
+        <v>112.0466026805547</v>
       </c>
       <c r="C2" t="n">
-        <v>40.44515620058616</v>
+        <v>45.64889896822883</v>
       </c>
       <c r="D2" t="n">
-        <v>5.469531280116788</v>
+        <v>7.14120115821786</v>
       </c>
       <c r="E2" t="n">
-        <v>3.249747414819828</v>
+        <v>4.085343527492916</v>
       </c>
       <c r="F2" t="n">
-        <v>10.25699074412656</v>
+        <v>2.844741888799267</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009189239151756474</v>
+        <v>0.3131998549984799</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9522189083119716</v>
+        <v>-0.0005089974318245905</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9613952996405052</v>
+        <v>-0.4952952494265003</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9840600407886628</v>
+        <v>-0.1103176749524275</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.00120402606575236</v>
+        <v>-0.0003855082596174151</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069729916277</v>
+        <v>-0.4809615599429674</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.05556724758627051</v>
+        <v>-0.005462621309446775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>34.84153929307306</v>
+        <v>99.99999997718767</v>
       </c>
       <c r="B3" t="n">
-        <v>114.4798639939993</v>
+        <v>116.0460748559863</v>
       </c>
       <c r="C3" t="n">
-        <v>40.76589219078036</v>
+        <v>45.88716767485425</v>
       </c>
       <c r="D3" t="n">
-        <v>7.553447585497219</v>
+        <v>5.684205555899331</v>
       </c>
       <c r="E3" t="n">
-        <v>3.530276020700602</v>
+        <v>4.628970721120143</v>
       </c>
       <c r="F3" t="n">
-        <v>2.760082041630822</v>
+        <v>10.36377349286016</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3828180862558426</v>
+        <v>0.009043526108662336</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0008745344714838011</v>
+        <v>-0.9457551987124372</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4956187866518041</v>
+        <v>-0.9564615448380345</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1094009664733735</v>
+        <v>-0.9811837046878377</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.001373671457423613</v>
+        <v>-1.598260301883177e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4813499804601892</v>
+        <v>-0.587499999837462</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07473776840000952</v>
+        <v>-0.05992403996668477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999999967758</v>
+        <v>36.46761472783696</v>
       </c>
       <c r="B4" t="n">
-        <v>90.18500985662632</v>
+        <v>111.3839620764843</v>
       </c>
       <c r="C4" t="n">
-        <v>40.44515620058616</v>
+        <v>45.64889896822883</v>
       </c>
       <c r="D4" t="n">
-        <v>5.469531280116788</v>
+        <v>7.14120115821786</v>
       </c>
       <c r="E4" t="n">
-        <v>3.262376382693733</v>
+        <v>4.085343527492916</v>
       </c>
       <c r="F4" t="n">
-        <v>10.25699074412656</v>
+        <v>2.844741888799267</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009189239151756474</v>
+        <v>0.3131998549984799</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9522189083119716</v>
+        <v>-0.0005089974318245905</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9613952996405052</v>
+        <v>-0.4952952494265003</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9840600407886628</v>
+        <v>-0.1103176749524275</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00120402606575236</v>
+        <v>-0.0003855082596174151</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069729916277</v>
+        <v>-0.4809615599429674</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05556724758627051</v>
+        <v>-0.005462621309446775</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>48.37291828725194</v>
+        <v>83.6957204987602</v>
       </c>
       <c r="B5" t="n">
-        <v>83.62069620300646</v>
+        <v>146.1480109636958</v>
       </c>
       <c r="C5" t="n">
-        <v>47.24533715319555</v>
+        <v>45.64617857497999</v>
       </c>
       <c r="D5" t="n">
-        <v>6.011479755896039</v>
+        <v>7.331867959392484</v>
       </c>
       <c r="E5" t="n">
-        <v>3.289790916607626</v>
+        <v>4.82189352882276</v>
       </c>
       <c r="F5" t="n">
-        <v>3.940274280905058</v>
+        <v>7.806850423182555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1093014744773693</v>
+        <v>0.01617895942620728</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6219365220615972</v>
+        <v>-0.9105289217154297</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.77211311796221</v>
+        <v>-0.9312176837260208</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7553274299992496</v>
+        <v>-0.9636004885159773</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.05605828148106486</v>
+        <v>-0.02045166216126157</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5711991756857593</v>
+        <v>-0.4713320085536663</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03326401639982051</v>
+        <v>-0.00484081713828341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50.65682388683794</v>
+        <v>46.53942563410952</v>
       </c>
       <c r="B6" t="n">
-        <v>92.84320129411002</v>
+        <v>96.4162420072532</v>
       </c>
       <c r="C6" t="n">
-        <v>40.74692338960718</v>
+        <v>45.72551164664051</v>
       </c>
       <c r="D6" t="n">
-        <v>6.199908016815032</v>
+        <v>6.565066455131624</v>
       </c>
       <c r="E6" t="n">
-        <v>4.077594104124731</v>
+        <v>3.70760659734656</v>
       </c>
       <c r="F6" t="n">
-        <v>4.223095434679305</v>
+        <v>3.802460686248752</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09218244640439374</v>
+        <v>0.1239267958069784</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6697769801294614</v>
+        <v>-0.5147401941033273</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7964933586643786</v>
+        <v>-0.7185483304579495</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7955258739510352</v>
+        <v>-0.659563868695147</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.04817474669628618</v>
+        <v>-0.07575736038903341</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5863644504284338</v>
+        <v>-0.5447496956826936</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07409808836376687</v>
+        <v>-0.02297409066068928</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>37.64166905875994</v>
+        <v>37.27342818942822</v>
       </c>
       <c r="B7" t="n">
-        <v>116.374847397049</v>
+        <v>124.325771987005</v>
       </c>
       <c r="C7" t="n">
-        <v>40.76479224928885</v>
+        <v>45.7200134502582</v>
       </c>
       <c r="D7" t="n">
-        <v>7.311881055132625</v>
+        <v>7.086025340243068</v>
       </c>
       <c r="E7" t="n">
-        <v>3.512822224007064</v>
+        <v>4.295589072400677</v>
       </c>
       <c r="F7" t="n">
-        <v>2.973385846555153</v>
+        <v>2.9121599126832</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2838990384663909</v>
+        <v>0.2879438039440393</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2059716642099542</v>
+        <v>-0.06336733853076429</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5796421880686904</v>
+        <v>-0.520490349023992</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3439726988899477</v>
+        <v>-0.1839720883888866</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.001920353592544704</v>
+        <v>-0.003960288568201895</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4999430156624669</v>
+        <v>-0.4860650451997121</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07470067535407957</v>
+        <v>-0.02171736005901745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>46.51664674729623</v>
+        <v>67.01209218639819</v>
       </c>
       <c r="B8" t="n">
-        <v>108.1514946902353</v>
+        <v>101.0572306781015</v>
       </c>
       <c r="C8" t="n">
-        <v>40.54983721873779</v>
+        <v>45.66149752294511</v>
       </c>
       <c r="D8" t="n">
-        <v>6.709344312727515</v>
+        <v>8.714795347086778</v>
       </c>
       <c r="E8" t="n">
-        <v>3.734592494866987</v>
+        <v>4.085586971136828</v>
       </c>
       <c r="F8" t="n">
-        <v>3.807714939110703</v>
+        <v>5.664860293256676</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1269092959002124</v>
+        <v>0.03503490402521764</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5755062911077844</v>
+        <v>-0.8303686183744579</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7485106255461088</v>
+        <v>-0.8806915876386617</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7145951106397391</v>
+        <v>-0.9151589206181028</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.06401985614579521</v>
+        <v>-0.03433728416219056</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5588734176047168</v>
+        <v>-0.3524611568280871</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06613944073923127</v>
+        <v>-0.008342290958882476</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62.81088985144039</v>
+        <v>87.2803039915933</v>
       </c>
       <c r="B9" t="n">
-        <v>141.9581033985354</v>
+        <v>110.3979519273781</v>
       </c>
       <c r="C9" t="n">
-        <v>40.78249223835885</v>
+        <v>45.6837838919623</v>
       </c>
       <c r="D9" t="n">
-        <v>9.631834935185067</v>
+        <v>7.281409826548456</v>
       </c>
       <c r="E9" t="n">
-        <v>3.290344952582981</v>
+        <v>3.672699068856347</v>
       </c>
       <c r="F9" t="n">
-        <v>5.280226884534877</v>
+        <v>8.377168330048841</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04539429484600108</v>
+        <v>0.01408469843958897</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8205251541929235</v>
+        <v>-0.9205286537835108</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8748656663625698</v>
+        <v>-0.9381104477659669</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9084180228809402</v>
+        <v>-0.9688685892988265</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.09793180218357037</v>
+        <v>-0.09118017196473958</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3442017269898631</v>
+        <v>-0.4968721659401022</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07529756756389346</v>
+        <v>-0.0134363181628111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40.23029325858423</v>
+        <v>69.70077915109846</v>
       </c>
       <c r="B10" t="n">
-        <v>114.9553830104288</v>
+        <v>101.0572306781015</v>
       </c>
       <c r="C10" t="n">
-        <v>40.37655149268871</v>
+        <v>45.66149752294511</v>
       </c>
       <c r="D10" t="n">
-        <v>7.285599986344494</v>
+        <v>8.714795347086778</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7879712732452</v>
+        <v>4.030250377893605</v>
       </c>
       <c r="F10" t="n">
-        <v>3.221662381859129</v>
+        <v>6.011294505035729</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2202750503695707</v>
+        <v>0.03050947471839705</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3479105616752287</v>
+        <v>-0.8485957172207006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6412699914997118</v>
+        <v>-0.8915240669949447</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.495076452861931</v>
+        <v>-0.9270092784300628</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.04854694074749431</v>
+        <v>-0.07819772966820576</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5171316407978435</v>
+        <v>-0.3716180514515766</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04719766501288245</v>
+        <v>-0.008342290958882476</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>42.64530641060869</v>
+        <v>48.17354385071194</v>
       </c>
       <c r="B11" t="n">
-        <v>90.85432643336603</v>
+        <v>114.7089422674158</v>
       </c>
       <c r="C11" t="n">
-        <v>42.47272999473714</v>
+        <v>47.51240831344352</v>
       </c>
       <c r="D11" t="n">
-        <v>6.779488398445778</v>
+        <v>6.057917054436489</v>
       </c>
       <c r="E11" t="n">
-        <v>3.352308439807675</v>
+        <v>3.893219091896589</v>
       </c>
       <c r="F11" t="n">
-        <v>3.402442652290079</v>
+        <v>3.952439896225221</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1760329876997892</v>
+        <v>0.1087977269066892</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4514929215304519</v>
+        <v>-0.5618235471157221</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6886341213751429</v>
+        <v>-0.7416239901379612</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5988488350263755</v>
+        <v>-0.7027463607309056</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02040273906746085</v>
+        <v>-0.002298078339400035</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5331674778150396</v>
+        <v>-0.5550991110545089</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01890291845863059</v>
+        <v>-0.4214809637465622</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41.87137413610396</v>
+        <v>57.17907125419582</v>
       </c>
       <c r="B12" t="n">
-        <v>90.85432643336603</v>
+        <v>107.0052061544893</v>
       </c>
       <c r="C12" t="n">
-        <v>42.2449374320328</v>
+        <v>45.69690797700385</v>
       </c>
       <c r="D12" t="n">
-        <v>6.806417895163603</v>
+        <v>9.05042933847586</v>
       </c>
       <c r="E12" t="n">
-        <v>3.194586328324944</v>
+        <v>4.877999812280802</v>
       </c>
       <c r="F12" t="n">
-        <v>3.323547611259765</v>
+        <v>4.570256330942689</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1886604200671399</v>
+        <v>0.06215261325291407</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4210022731895705</v>
+        <v>-0.7338110109505044</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6744867543475873</v>
+        <v>-0.8285207790621435</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5689549564970953</v>
+        <v>-0.8463578351961917</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.002141937360115366</v>
+        <v>-0.001916479082161475</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.528028519542327</v>
+        <v>-0.3038430344064686</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03052410115034751</v>
+        <v>-0.01643610902945222</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>78.45799805877661</v>
+        <v>45.50228243051699</v>
       </c>
       <c r="B13" t="n">
-        <v>104.1602635518476</v>
+        <v>72.48584052497696</v>
       </c>
       <c r="C13" t="n">
-        <v>40.47184849630636</v>
+        <v>46.37674432666019</v>
       </c>
       <c r="D13" t="n">
-        <v>7.949692479550971</v>
+        <v>6.156470597324431</v>
       </c>
       <c r="E13" t="n">
-        <v>3.678437416206426</v>
+        <v>4.095279403251187</v>
       </c>
       <c r="F13" t="n">
-        <v>7.069967090149865</v>
+        <v>3.629675314229103</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02055917431937372</v>
+        <v>0.134469575006216</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9055761456413484</v>
+        <v>-0.4840657622657086</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9278395244844816</v>
+        <v>-0.7044443584635034</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9608633777008292</v>
+        <v>-0.6312840578478263</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.02908495421702676</v>
+        <v>-0.002589818814799248</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4610867163705868</v>
+        <v>-0.55334854953678</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.05936308250626037</v>
+        <v>-0.1718272746651878</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>39.15537346967218</v>
+        <v>58.93026058056421</v>
       </c>
       <c r="B14" t="n">
-        <v>104.8853510818438</v>
+        <v>105.825800807257</v>
       </c>
       <c r="C14" t="n">
-        <v>40.37655149268871</v>
+        <v>46.38685690093838</v>
       </c>
       <c r="D14" t="n">
-        <v>7.26752877173799</v>
+        <v>9.05042933847586</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7879712732452</v>
+        <v>4.684872532354102</v>
       </c>
       <c r="F14" t="n">
-        <v>3.112233124619191</v>
+        <v>4.784369399372701</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2441472648808752</v>
+        <v>0.05576735195749526</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2935290831317897</v>
+        <v>-0.7562054303704098</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6172713060412822</v>
+        <v>-0.8402678740958728</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4383613151801181</v>
+        <v>-0.8632446474182944</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01733970239898831</v>
+        <v>-0.0440484304465403</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5099941067736072</v>
+        <v>-0.3169769543542316</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.04719766501288245</v>
+        <v>-0.1741387202144877</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>74.50777289111103</v>
+        <v>36.48801030984511</v>
       </c>
       <c r="B15" t="n">
-        <v>125.1899424666051</v>
+        <v>112.0484475154796</v>
       </c>
       <c r="C15" t="n">
-        <v>41.06005536382583</v>
+        <v>45.64778452219159</v>
       </c>
       <c r="D15" t="n">
-        <v>9.862330989653444</v>
+        <v>7.14120115821786</v>
       </c>
       <c r="E15" t="n">
-        <v>3.287469667035815</v>
+        <v>4.684913219530513</v>
       </c>
       <c r="F15" t="n">
-        <v>6.832032557485642</v>
+        <v>2.846583079565492</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02489968417761925</v>
+        <v>0.3125289296548622</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8901876546797023</v>
+        <v>-0.002167057857864165</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9174391395684948</v>
+        <v>-0.495953760995105</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9521804742522989</v>
+        <v>-0.1122802727744542</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3188801411055618</v>
+        <v>-0.0008007611318502547</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4315782589191596</v>
+        <v>-0.4810907319623524</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.08465775793845629</v>
+        <v>-0.00520789078664971</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36.20770487245836</v>
+        <v>64.21693107853231</v>
       </c>
       <c r="B16" t="n">
-        <v>111.5039091236182</v>
+        <v>120.6148796905972</v>
       </c>
       <c r="C16" t="n">
-        <v>40.7678246795919</v>
+        <v>45.67068984414236</v>
       </c>
       <c r="D16" t="n">
-        <v>7.490588920324285</v>
+        <v>9.006115022959786</v>
       </c>
       <c r="E16" t="n">
-        <v>3.599002352827596</v>
+        <v>4.623547034026672</v>
       </c>
       <c r="F16" t="n">
-        <v>2.870853600411424</v>
+        <v>5.367339102946453</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3299926373378083</v>
+        <v>0.04086127419525665</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1087620294542204</v>
+        <v>-0.807938943624518</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5391349469316234</v>
+        <v>-0.8676986943311426</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2349978977131068</v>
+        <v>-0.8999758788557481</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01601316664807963</v>
+        <v>-0.05310041020601276</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4904214045852135</v>
+        <v>-0.3325456339345426</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07480293722653204</v>
+        <v>-0.01044339294682506</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80.50591501711548</v>
+        <v>79.194756620433</v>
       </c>
       <c r="B17" t="n">
-        <v>109.799205878415</v>
+        <v>120.2187206698072</v>
       </c>
       <c r="C17" t="n">
-        <v>40.76486714428681</v>
+        <v>48.01594704044896</v>
       </c>
       <c r="D17" t="n">
-        <v>7.924082420366796</v>
+        <v>7.590481089147817</v>
       </c>
       <c r="E17" t="n">
-        <v>4.442906228774013</v>
+        <v>4.371589404573928</v>
       </c>
       <c r="F17" t="n">
-        <v>7.370462777000927</v>
+        <v>7.223112069271777</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01884060505084268</v>
+        <v>0.01955278306991936</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.912230796583794</v>
+        <v>-0.8951880026531811</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9323524366095689</v>
+        <v>-0.9208952957941127</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9644621853373564</v>
+        <v>-0.9551306453092572</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07712530513242727</v>
+        <v>-0.0386680313009321</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4763847988505056</v>
+        <v>-0.4392626409205851</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.07470320101896309</v>
+        <v>-0.1337445483148776</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36.86310923512347</v>
+        <v>80.94990125209702</v>
       </c>
       <c r="B18" t="n">
-        <v>111.4983224522373</v>
+        <v>120.2187206698072</v>
       </c>
       <c r="C18" t="n">
-        <v>40.76479090225769</v>
+        <v>48.01594704044896</v>
       </c>
       <c r="D18" t="n">
-        <v>7.405881501714024</v>
+        <v>7.590481089147817</v>
       </c>
       <c r="E18" t="n">
-        <v>3.468684115650316</v>
+        <v>4.388961752283821</v>
       </c>
       <c r="F18" t="n">
-        <v>2.916530958857637</v>
+        <v>7.488020935211635</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3078101037549479</v>
+        <v>0.01816058288383836</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1550757142744112</v>
+        <v>-0.9015284491417312</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5582742164304054</v>
+        <v>-0.9250916255236283</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2874396477391212</v>
+        <v>-0.958679430191443</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.008750052974593045</v>
+        <v>-0.07451388280709643</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4947733301766939</v>
+        <v>-0.4517680464211913</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.07470062992849168</v>
+        <v>-0.1337445483148776</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>84.70112940131075</v>
+        <v>42.28065622474105</v>
       </c>
       <c r="B19" t="n">
-        <v>103.8935315683946</v>
+        <v>122.6169530873122</v>
       </c>
       <c r="C19" t="n">
-        <v>40.79726927549989</v>
+        <v>45.64051735752375</v>
       </c>
       <c r="D19" t="n">
-        <v>7.553266573602467</v>
+        <v>6.78887570090826</v>
       </c>
       <c r="E19" t="n">
-        <v>3.524651229583902</v>
+        <v>4.091848583616914</v>
       </c>
       <c r="F19" t="n">
-        <v>7.958713051150809</v>
+        <v>3.361884209548128</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01586023889533447</v>
+        <v>0.1778947445378279</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9239987160509262</v>
+        <v>-0.3555884917294968</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9405469516303439</v>
+        <v>-0.6446043329924097</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9706127035509579</v>
+        <v>-0.5037215201071105</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.09185216417081683</v>
+        <v>-0.03251455222022308</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5077233428324929</v>
+        <v>-0.51777748942336</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07579588981249732</v>
+        <v>-0.003546824576856483</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>38.35330827777208</v>
+        <v>41.68485315296074</v>
       </c>
       <c r="B20" t="n">
-        <v>114.9553830104288</v>
+        <v>122.5119694030566</v>
       </c>
       <c r="C20" t="n">
-        <v>40.47517995865881</v>
+        <v>45.65303472981122</v>
       </c>
       <c r="D20" t="n">
-        <v>7.285599986344494</v>
+        <v>6.806835545328163</v>
       </c>
       <c r="E20" t="n">
-        <v>3.7879712732452</v>
+        <v>4.731217926333255</v>
       </c>
       <c r="F20" t="n">
-        <v>3.03647439094767</v>
+        <v>3.302276183398194</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2642212579381667</v>
+        <v>0.1877179438454561</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2488690337813602</v>
+        <v>-0.3279429475418421</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5979304072379608</v>
+        <v>-0.6322896914584664</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.390678277480787</v>
+        <v>-0.4752247044427014</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.004963040397104867</v>
+        <v>-0.02374553432228646</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.50466834418565</v>
+        <v>-0.5140040699687514</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.05976186414752666</v>
+        <v>-0.006407938242563443</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>59.78297539615504</v>
+        <v>97.8090492551828</v>
       </c>
       <c r="B21" t="n">
-        <v>138.1746253589715</v>
+        <v>117.2261772177501</v>
       </c>
       <c r="C21" t="n">
-        <v>40.78249223835885</v>
+        <v>45.9051382014301</v>
       </c>
       <c r="D21" t="n">
-        <v>9.653160148800273</v>
+        <v>6.009103048809155</v>
       </c>
       <c r="E21" t="n">
-        <v>3.248364162284755</v>
+        <v>3.806681490963482</v>
       </c>
       <c r="F21" t="n">
-        <v>4.936461660202545</v>
+        <v>10.00937295956612</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0542761257915252</v>
+        <v>0.009707230044989704</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7928157536809788</v>
+        <v>-0.9423026149832401</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8591349295212989</v>
+        <v>-0.9538638457218076</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8892295894832911</v>
+        <v>-0.9795903373136583</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.05464223779498292</v>
+        <v>-0.03094194543318851</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3215829948725871</v>
+        <v>-0.5718894759431774</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.07529756756389346</v>
+        <v>-0.06403158889830771</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>35.80984505547272</v>
+        <v>72.00167083499721</v>
       </c>
       <c r="B22" t="n">
-        <v>103.8935315683946</v>
+        <v>123.0365580077285</v>
       </c>
       <c r="C22" t="n">
-        <v>40.79726927549989</v>
+        <v>45.72001071955749</v>
       </c>
       <c r="D22" t="n">
-        <v>7.553266573602467</v>
+        <v>8.255565873594366</v>
       </c>
       <c r="E22" t="n">
-        <v>3.53058231521825</v>
+        <v>4.501371594014029</v>
       </c>
       <c r="F22" t="n">
-        <v>2.84634938677772</v>
+        <v>6.244832074729795</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3445139425551811</v>
+        <v>0.02714725288598421</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.07894266117122917</v>
+        <v>-0.8622530658222185</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5269530720259915</v>
+        <v>-0.899915591184312</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2007390624105867</v>
+        <v>-0.9356059275925527</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.02395249273914486</v>
+        <v>-0.0161410857224546</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4877795907402145</v>
+        <v>-0.3880119046993551</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.07579588981249732</v>
+        <v>-0.02171673589885389</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35.54312470793869</v>
+        <v>60.89316748042043</v>
       </c>
       <c r="B23" t="n">
-        <v>106.510472646307</v>
+        <v>105.825800807257</v>
       </c>
       <c r="C23" t="n">
-        <v>40.76766991030113</v>
+        <v>45.69690797700385</v>
       </c>
       <c r="D23" t="n">
-        <v>7.491339031368922</v>
+        <v>9.05042933847586</v>
       </c>
       <c r="E23" t="n">
-        <v>3.842052955145039</v>
+        <v>4.685382696973211</v>
       </c>
       <c r="F23" t="n">
-        <v>2.811490668252719</v>
+        <v>4.983562679888059</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3543406345536074</v>
+        <v>0.04946602089399922</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.05840062767321195</v>
+        <v>-0.7758052485051592</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.51865805650542</v>
+        <v>-0.8497964207098053</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1769777352202081</v>
+        <v>-0.8772163272530668</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0009403643423211749</v>
+        <v>-0.01257767073410864</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4860085511006828</v>
+        <v>-0.3088638182979955</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.07479771798127693</v>
+        <v>-0.01643610902945222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>45.61146828249585</v>
+        <v>73.56046327032763</v>
       </c>
       <c r="B24" t="n">
-        <v>100.4530131093344</v>
+        <v>121.5997401044346</v>
       </c>
       <c r="C24" t="n">
-        <v>40.77955921009013</v>
+        <v>45.65409209409685</v>
       </c>
       <c r="D24" t="n">
-        <v>6.666201530882267</v>
+        <v>8.653694021295577</v>
       </c>
       <c r="E24" t="n">
-        <v>3.408314488437455</v>
+        <v>3.406056845598668</v>
       </c>
       <c r="F24" t="n">
-        <v>3.694967276138202</v>
+        <v>6.52215651465714</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1365221355737509</v>
+        <v>0.02528325330745377</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.550272396867689</v>
+        <v>-0.8703712625345413</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7360092145926435</v>
+        <v>-0.9049050748520345</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6918631957175402</v>
+        <v>-0.9405632973757075</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.03098851543789887</v>
+        <v>-0.1288643712420658</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5528629764935175</v>
+        <v>-0.3991183008010843</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.07519865780085162</v>
+        <v>-0.006649621507852504</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>59.93796189021795</v>
+        <v>50.97653780471558</v>
       </c>
       <c r="B25" t="n">
-        <v>123.9737470966107</v>
+        <v>120.6437849958725</v>
       </c>
       <c r="C25" t="n">
-        <v>41.23379988611082</v>
+        <v>45.7205328324451</v>
       </c>
       <c r="D25" t="n">
-        <v>9.760975171653044</v>
+        <v>9.668557530235331</v>
       </c>
       <c r="E25" t="n">
-        <v>3.285180162001424</v>
+        <v>4.367100651185702</v>
       </c>
       <c r="F25" t="n">
-        <v>4.989433185494332</v>
+        <v>4.040515548612358</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05388304931297774</v>
+        <v>0.09554912287459774</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7942639871896554</v>
+        <v>-0.6220748984746126</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8599004634612719</v>
+        <v>-0.7702497576662741</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8902390128047444</v>
+        <v>-0.7544158192495142</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.08768952716572501</v>
+        <v>-0.003351618656515407</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.322740754790436</v>
+        <v>-0.2382078318585985</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.08935457609651613</v>
+        <v>-0.02183607598745252</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>72.82181803037648</v>
+        <v>38.27989065739488</v>
       </c>
       <c r="B26" t="n">
-        <v>126.0083072033538</v>
+        <v>111.4114263107169</v>
       </c>
       <c r="C26" t="n">
-        <v>39.06451772036475</v>
+        <v>45.68160126051698</v>
       </c>
       <c r="D26" t="n">
-        <v>9.760508232024044</v>
+        <v>7.008362414746505</v>
       </c>
       <c r="E26" t="n">
-        <v>3.450330780253116</v>
+        <v>4.374661341111648</v>
       </c>
       <c r="F26" t="n">
-        <v>6.575962785578109</v>
+        <v>2.993964736444236</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02692765773418521</v>
+        <v>0.2598895173372955</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8827893480836856</v>
+        <v>-0.1346798562927683</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9126726852745606</v>
+        <v>-0.5496595068281946</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9478809767583574</v>
+        <v>-0.2655738208685782</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2425094435312339</v>
+        <v>-0.003455821268681355</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4189840585479406</v>
+        <v>-0.4924393074968343</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.05549726280862397</v>
+        <v>-0.01293743097530969</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87.71238109979888</v>
+        <v>76.90921921709023</v>
       </c>
       <c r="B27" t="n">
-        <v>89.6271047543792</v>
+        <v>120.6187163453363</v>
       </c>
       <c r="C27" t="n">
-        <v>40.76672982236553</v>
+        <v>45.9736520715886</v>
       </c>
       <c r="D27" t="n">
-        <v>7.107409767831828</v>
+        <v>8.036693338227479</v>
       </c>
       <c r="E27" t="n">
-        <v>3.728479656367004</v>
+        <v>4.61101403797515</v>
       </c>
       <c r="F27" t="n">
-        <v>8.36996748298292</v>
+        <v>6.904896669738123</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01409678419996886</v>
+        <v>0.02161246216094752</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9311441953330922</v>
+        <v>-0.8860258896096588</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9456642270530528</v>
+        <v>-0.9149191870579304</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.974203178287992</v>
+        <v>-0.9498756275098333</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.06022666066894877</v>
+        <v>-0.06103508009695766</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5302176029946006</v>
+        <v>-0.4229781869217678</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.07476601563597676</v>
+        <v>-0.07969190207739299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97.0010678137303</v>
+        <v>91.69910214349393</v>
       </c>
       <c r="B28" t="n">
-        <v>106.510472646307</v>
+        <v>120.5665871532924</v>
       </c>
       <c r="C28" t="n">
-        <v>40.462398155512</v>
+        <v>45.6492848308424</v>
       </c>
       <c r="D28" t="n">
-        <v>7.479259884047645</v>
+        <v>6.990132645686027</v>
       </c>
       <c r="E28" t="n">
-        <v>3.239513249094351</v>
+        <v>4.598466271662956</v>
       </c>
       <c r="F28" t="n">
-        <v>10.03599603930799</v>
+        <v>9.073777322665849</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01020352237330908</v>
+        <v>0.01197579475734051</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9479147793493211</v>
+        <v>-0.9308527608543955</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9580086484627041</v>
+        <v>-0.9454405871004407</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9821351057069995</v>
+        <v>-0.9740883689118659</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.3872643424377638</v>
+        <v>-0.1250268663758971</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5996047404472388</v>
+        <v>-0.5283561027723942</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.05809981749806401</v>
+        <v>-0.005550818478264469</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>82.10624370772818</v>
+        <v>43.00012211442329</v>
       </c>
       <c r="B29" t="n">
-        <v>104.2699095952507</v>
+        <v>122.5862286945539</v>
       </c>
       <c r="C29" t="n">
-        <v>40.75565832534479</v>
+        <v>45.63850010740611</v>
       </c>
       <c r="D29" t="n">
-        <v>7.980184799423136</v>
+        <v>6.826135990672662</v>
       </c>
       <c r="E29" t="n">
-        <v>3.628927191351822</v>
+        <v>4.153712711824051</v>
       </c>
       <c r="F29" t="n">
-        <v>7.622882133302253</v>
+        <v>3.445059712932152</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01764076698251028</v>
+        <v>0.1669829478680921</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.916973845994251</v>
+        <v>-0.3869008913799948</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9356081017611474</v>
+        <v>-0.6587122468315487</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9669730047010342</v>
+        <v>-0.5354960423978661</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1262920562636999</v>
+        <v>-0.05994287960871346</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.4883393657602065</v>
+        <v>-0.5223341067246807</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.07439265437024253</v>
+        <v>-0.003085738835682389</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>38.21058354658026</v>
+        <v>55.1580988103015</v>
       </c>
       <c r="B30" t="n">
-        <v>125.3740500207897</v>
+        <v>120.6403500318956</v>
       </c>
       <c r="C30" t="n">
-        <v>40.76479224928885</v>
+        <v>45.71995966379404</v>
       </c>
       <c r="D30" t="n">
-        <v>7.311881055132625</v>
+        <v>9.592206984201162</v>
       </c>
       <c r="E30" t="n">
-        <v>3.512822224007064</v>
+        <v>4.288682158093827</v>
       </c>
       <c r="F30" t="n">
-        <v>3.027216106489051</v>
+        <v>4.446208537654092</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2680788897175146</v>
+        <v>0.07131493511744355</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2404882980236231</v>
+        <v>-0.7002383970438542</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5943300582145686</v>
+        <v>-0.8100013181803668</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3816124283677981</v>
+        <v>-0.8194475370986681</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.01563563123293859</v>
+        <v>-0.04382568208964508</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5037206431241479</v>
+        <v>-0.2680014540233981</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.07470067535407957</v>
+        <v>-0.02170506601006525</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>44.71412679424434</v>
+        <v>41.0353891735891</v>
       </c>
       <c r="B31" t="n">
-        <v>103.6177625217911</v>
+        <v>80.87513331766179</v>
       </c>
       <c r="C31" t="n">
-        <v>40.77180383555397</v>
+        <v>45.6510033686884</v>
       </c>
       <c r="D31" t="n">
-        <v>6.671166635183724</v>
+        <v>6.806835545328163</v>
       </c>
       <c r="E31" t="n">
-        <v>3.529891979485741</v>
+        <v>4.356669834227053</v>
       </c>
       <c r="F31" t="n">
-        <v>3.594470516589437</v>
+        <v>3.234715065216244</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1470711365161859</v>
+        <v>0.1992047708005867</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5231676567578037</v>
+        <v>-0.2995037706737928</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7227714693760475</v>
+        <v>-0.6204337224330028</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6669641666475905</v>
+        <v>-0.446381188031051</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.006282748005365344</v>
+        <v>-0.03390275822335841</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5469045733923554</v>
+        <v>-0.516730029628329</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07493712528653625</v>
+        <v>-0.005943627128776607</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>43.6137976492699</v>
+        <v>44.20015360877245</v>
       </c>
       <c r="B32" t="n">
-        <v>110.2276238800381</v>
+        <v>120.8065157768257</v>
       </c>
       <c r="C32" t="n">
-        <v>40.52405991697522</v>
+        <v>45.64827029363628</v>
       </c>
       <c r="D32" t="n">
-        <v>6.806552273678734</v>
+        <v>6.517532426827063</v>
       </c>
       <c r="E32" t="n">
-        <v>3.697488868464889</v>
+        <v>3.70445705618001</v>
       </c>
       <c r="F32" t="n">
-        <v>3.496693783284605</v>
+        <v>3.526084187349859</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1616752188337212</v>
+        <v>0.1502089557468833</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4867085522954692</v>
+        <v>-0.4350758001416055</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7052435797728811</v>
+        <v>-0.6808779150867821</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6327042000008322</v>
+        <v>-0.5834182622634835</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.008766250948177826</v>
+        <v>-0.000231594445431643</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.5395983196689379</v>
+        <v>-0.5299343061888921</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.06434475449516448</v>
+        <v>-0.005318924259720831</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>71.94413129290558</v>
+        <v>52.57503451192947</v>
       </c>
       <c r="B33" t="n">
-        <v>114.390001952247</v>
+        <v>120.5958724481185</v>
       </c>
       <c r="C33" t="n">
-        <v>40.46946232868888</v>
+        <v>45.6763151082325</v>
       </c>
       <c r="D33" t="n">
-        <v>8.580364257795154</v>
+        <v>9.602952622632596</v>
       </c>
       <c r="E33" t="n">
-        <v>3.527006299973762</v>
+        <v>4.494981098917195</v>
       </c>
       <c r="F33" t="n">
-        <v>6.257317905492803</v>
+        <v>4.184194123564119</v>
       </c>
       <c r="G33" t="n">
-        <v>0.02782305196897841</v>
+        <v>0.08512661983193348</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8789427719898126</v>
+        <v>-0.6549372583339659</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9103671657937108</v>
+        <v>-0.7874730140573284</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9456422235847406</v>
+        <v>-0.7823677155035599</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.03682774269038028</v>
+        <v>-0.01029046420577741</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.4124276774179891</v>
+        <v>-0.2495971208974975</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.05907745423309888</v>
+        <v>-0.01172916759600032</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>64.89631627224227</v>
+        <v>37.64451932741748</v>
       </c>
       <c r="B34" t="n">
-        <v>106.9111674102627</v>
+        <v>108.37585119112</v>
       </c>
       <c r="C34" t="n">
-        <v>40.76741611520529</v>
+        <v>45.71769409509987</v>
       </c>
       <c r="D34" t="n">
-        <v>9.427200876654561</v>
+        <v>7.07083917035349</v>
       </c>
       <c r="E34" t="n">
-        <v>3.844034633493088</v>
+        <v>4.697353444481298</v>
       </c>
       <c r="F34" t="n">
-        <v>5.495049877126664</v>
+        <v>2.944537603148461</v>
       </c>
       <c r="G34" t="n">
-        <v>0.04030453911317519</v>
+        <v>0.2772042540944994</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8368023504236217</v>
+        <v>-0.09052342114808479</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8844232532539466</v>
+        <v>-0.5315184926214909</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9192615689289938</v>
+        <v>-0.2152918169994476</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.09223926580146191</v>
+        <v>-0.00777806130489408</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.3597800077699131</v>
+        <v>-0.4884152890736441</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.07478915931409351</v>
+        <v>-0.02118722173711327</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55.85797819029698</v>
+        <v>39.09352527873338</v>
       </c>
       <c r="B35" t="n">
-        <v>117.9286319089528</v>
+        <v>119.0041671681926</v>
       </c>
       <c r="C35" t="n">
-        <v>41.06005562095125</v>
+        <v>45.64913131096276</v>
       </c>
       <c r="D35" t="n">
-        <v>9.989007457647428</v>
+        <v>6.983094114771444</v>
       </c>
       <c r="E35" t="n">
-        <v>3.290344952582981</v>
+        <v>4.639109143478006</v>
       </c>
       <c r="F35" t="n">
-        <v>4.578451192085003</v>
+        <v>3.068102942799833</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0698492639206974</v>
+        <v>0.23981103341305</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7471891137632554</v>
+        <v>-0.1870295720182997</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.834275253134909</v>
+        <v>-0.5714865762475844</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8557421465966751</v>
+        <v>-0.3240648365668646</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.06599783974851212</v>
+        <v>-0.01386610869507745</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2922629920550063</v>
+        <v>-0.4975923267653114</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.08465776660943111</v>
+        <v>-0.005515728220059357</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>39.75280986265456</v>
+        <v>88.54967150064394</v>
       </c>
       <c r="B36" t="n">
-        <v>91.57723603871595</v>
+        <v>120.4283646544664</v>
       </c>
       <c r="C36" t="n">
-        <v>41.0923924041474</v>
+        <v>45.6813646298513</v>
       </c>
       <c r="D36" t="n">
-        <v>7.209271035287077</v>
+        <v>7.003004604023305</v>
       </c>
       <c r="E36" t="n">
-        <v>3.596194821147103</v>
+        <v>4.352030463023146</v>
       </c>
       <c r="F36" t="n">
-        <v>3.169833872042054</v>
+        <v>8.541674676917243</v>
       </c>
       <c r="G36" t="n">
-        <v>0.23045636202848</v>
+        <v>0.01341435392565342</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3244975682187208</v>
+        <v>-0.9237290535949821</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6308778959186407</v>
+        <v>-0.9403765446891724</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.4708481696090121</v>
+        <v>-0.9705140489327674</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0334143211387891</v>
+        <v>-0.0495554986033899</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5139611214534138</v>
+        <v>-0.505916409442088</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.08574825168848382</v>
+        <v>-0.01288334396601171</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>51.7106563027797</v>
+        <v>43.42695205970158</v>
       </c>
       <c r="B37" t="n">
-        <v>106.8287305184614</v>
+        <v>114.7190177630041</v>
       </c>
       <c r="C37" t="n">
-        <v>40.64388577428083</v>
+        <v>45.63808802558109</v>
       </c>
       <c r="D37" t="n">
-        <v>6.410160005966915</v>
+        <v>6.777580241796441</v>
       </c>
       <c r="E37" t="n">
-        <v>3.466522731072767</v>
+        <v>3.783352054627115</v>
       </c>
       <c r="F37" t="n">
-        <v>4.39342269946061</v>
+        <v>3.483428934984896</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08559229198084864</v>
+        <v>0.1608282709860549</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6889962876459454</v>
+        <v>-0.4045856847573953</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8061723710176664</v>
+        <v>-0.6667805264034268</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8111377159339529</v>
+        <v>-0.5532248972637828</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1403507063949165</v>
+        <v>-0.05664857232774966</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.5933619629891063</v>
+        <v>-0.5250373630447767</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.07019424997349825</v>
+        <v>-0.002991548704249641</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>43.7275474976427</v>
+        <v>44.66789280247933</v>
       </c>
       <c r="B38" t="n">
-        <v>110.2276238800381</v>
+        <v>94.8323680542761</v>
       </c>
       <c r="C38" t="n">
-        <v>40.52405991697522</v>
+        <v>46.58055881910004</v>
       </c>
       <c r="D38" t="n">
-        <v>6.816429046841734</v>
+        <v>6.565066455131624</v>
       </c>
       <c r="E38" t="n">
-        <v>3.697488868464889</v>
+        <v>3.770050837266156</v>
       </c>
       <c r="F38" t="n">
-        <v>3.510717798425854</v>
+        <v>3.60816428227474</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1601115492019649</v>
+        <v>0.1446006309424632</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4906275970461073</v>
+        <v>-0.4521875715743809</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7071069952775223</v>
+        <v>-0.6888101241899535</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6364222084663805</v>
+        <v>-0.6000573711559398</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.01480364939419163</v>
+        <v>-0.04586077841593264</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5403536257125957</v>
+        <v>-0.5328966544157023</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.06434475449516448</v>
+        <v>-0.2184134443657242</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96.28852350797513</v>
+        <v>54.33016763501264</v>
       </c>
       <c r="B39" t="n">
-        <v>123.9115384300012</v>
+        <v>120.6403500318956</v>
       </c>
       <c r="C39" t="n">
-        <v>40.35994969789353</v>
+        <v>45.71995693309333</v>
       </c>
       <c r="D39" t="n">
-        <v>5.980634385985652</v>
+        <v>9.56541848365174</v>
       </c>
       <c r="E39" t="n">
-        <v>3.491736596028943</v>
+        <v>4.494981098917195</v>
       </c>
       <c r="F39" t="n">
-        <v>9.660950836507999</v>
+        <v>4.356364841342318</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01037462821627083</v>
+        <v>0.07537607687311615</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9469509431437005</v>
+        <v>-0.6866692616130882</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9573624154176801</v>
+        <v>-0.8031837822275355</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9817069796537896</v>
+        <v>-0.8085266048070273</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.01091627488348043</v>
+        <v>-0.02726058869652128</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.5942819847975758</v>
+        <v>-0.2621024443994651</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.04517264235369641</v>
+        <v>-0.02170444184990419</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>90.21091327590622</v>
+        <v>75.79003913105004</v>
       </c>
       <c r="B40" t="n">
-        <v>90.85432643336603</v>
+        <v>124.1591203193065</v>
       </c>
       <c r="C40" t="n">
-        <v>42.418766969033</v>
+        <v>45.96448538877763</v>
       </c>
       <c r="D40" t="n">
-        <v>6.806417895163603</v>
+        <v>8.120248385748285</v>
       </c>
       <c r="E40" t="n">
-        <v>3.352308439807675</v>
+        <v>4.61101403797515</v>
       </c>
       <c r="F40" t="n">
-        <v>8.750529929526493</v>
+        <v>6.757389950262268</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01284691438407032</v>
+        <v>0.02273542779976698</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9363597973656501</v>
+        <v>-0.881124960104218</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9494545513684846</v>
+        <v>-0.9117647334751466</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9767475974960156</v>
+        <v>-0.9470058472408119</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.09024750456653018</v>
+        <v>-0.05916239580121511</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5488818125726221</v>
+        <v>-0.4150040288087316</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0221059255596125</v>
+        <v>-0.07759666029202889</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>94.07297970598101</v>
+        <v>38.8842724212424</v>
       </c>
       <c r="B41" t="n">
-        <v>104.522104840114</v>
+        <v>119.0041671681926</v>
       </c>
       <c r="C41" t="n">
-        <v>40.76594450642119</v>
+        <v>45.64913131096276</v>
       </c>
       <c r="D41" t="n">
-        <v>6.374124250000767</v>
+        <v>6.987004850110982</v>
       </c>
       <c r="E41" t="n">
-        <v>3.486394690053881</v>
+        <v>4.626903054095624</v>
       </c>
       <c r="F41" t="n">
-        <v>9.330758252124102</v>
+        <v>3.048240977136164</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01119365536965436</v>
+        <v>0.2447701408684471</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9433971337851508</v>
+        <v>-0.1739884316314205</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9546760807582878</v>
+        <v>-0.566014806253461</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9800753234339468</v>
+        <v>-0.3096090267245313</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.05875871040059433</v>
+        <v>-0.01025919719441624</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.5777317181069426</v>
+        <v>-0.4962670586678685</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.07473953262700107</v>
+        <v>-0.005515728220059357</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96.330859351131</v>
+        <v>64.892614450322</v>
       </c>
       <c r="B42" t="n">
-        <v>106.5766365971351</v>
+        <v>121.5753465433478</v>
       </c>
       <c r="C42" t="n">
-        <v>40.76594450642119</v>
+        <v>46.15439975650749</v>
       </c>
       <c r="D42" t="n">
-        <v>6.164706004781737</v>
+        <v>8.736018851505738</v>
       </c>
       <c r="E42" t="n">
-        <v>3.486394690053881</v>
+        <v>4.49731874250808</v>
       </c>
       <c r="F42" t="n">
-        <v>9.698424668570716</v>
+        <v>5.420362995120236</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01036884531609364</v>
+        <v>0.03930245758761455</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.9470022343762685</v>
+        <v>-0.8137631268247766</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.957390943703703</v>
+        <v>-0.8710533410127481</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9817292410008477</v>
+        <v>-0.903984254329942</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.0798612822733426</v>
+        <v>-0.01509542581520803</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5945982364980261</v>
+        <v>-0.3373598779585442</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.07473953262700107</v>
+        <v>-0.1210056586302825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>54.84504996866246</v>
+        <v>38.43709693420806</v>
       </c>
       <c r="B43" t="n">
-        <v>117.4786725699016</v>
+        <v>111.0958501314078</v>
       </c>
       <c r="C43" t="n">
-        <v>40.9566407065628</v>
+        <v>45.68374956647192</v>
       </c>
       <c r="D43" t="n">
-        <v>9.777794488313841</v>
+        <v>6.983870022236546</v>
       </c>
       <c r="E43" t="n">
-        <v>3.350927908811135</v>
+        <v>3.672699068856347</v>
       </c>
       <c r="F43" t="n">
-        <v>4.434364619511899</v>
+        <v>3.005146418402903</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07452948834554815</v>
+        <v>0.2558051783809665</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.7334544456815553</v>
+        <v>-0.1451702783751325</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.8271109105826757</v>
+        <v>-0.5540086402098064</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.8452818744871318</v>
+        <v>-0.2773993035812902</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.007551499006029375</v>
+        <v>-5.306522470436901e-05</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.284696347607972</v>
+        <v>-0.4934349472499844</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.08117033186961718</v>
+        <v>-0.01342847233644029</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>35.18232948564541</v>
+        <v>40.66579495331204</v>
       </c>
       <c r="B44" t="n">
-        <v>117.4832416076467</v>
+        <v>118.9476382587276</v>
       </c>
       <c r="C44" t="n">
-        <v>40.4654364521018</v>
+        <v>45.64913131096276</v>
       </c>
       <c r="D44" t="n">
-        <v>7.584339410569404</v>
+        <v>6.983094114771444</v>
       </c>
       <c r="E44" t="n">
-        <v>3.398771680051238</v>
+        <v>4.638855086362049</v>
       </c>
       <c r="F44" t="n">
-        <v>2.794569822327461</v>
+        <v>3.225689201862419</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3688231948542672</v>
+        <v>0.2064523455197652</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.02928544819772175</v>
+        <v>-0.2766439337728725</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.506932198109642</v>
+        <v>-0.6097599326745485</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.1429147817111795</v>
+        <v>-0.4212706096856652</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.009852017585574946</v>
+        <v>-0.04927985796085809</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.4836128484617849</v>
+        <v>-0.5075500347043096</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0585460951133073</v>
+        <v>-0.005515728220059357</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>41.87137413610396</v>
+        <v>48.85031795907724</v>
       </c>
       <c r="B45" t="n">
-        <v>90.85432643336603</v>
+        <v>110.6194135759527</v>
       </c>
       <c r="C45" t="n">
-        <v>42.2449374320328</v>
+        <v>47.51240831344352</v>
       </c>
       <c r="D45" t="n">
-        <v>6.806417895163603</v>
+        <v>6.057917054436489</v>
       </c>
       <c r="E45" t="n">
-        <v>3.284821228246241</v>
+        <v>4.601326734809483</v>
       </c>
       <c r="F45" t="n">
-        <v>3.323547611259765</v>
+        <v>4.034954754125128</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1886604200671399</v>
+        <v>0.1033222111422846</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4210022731895705</v>
+        <v>-0.5794407998520332</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6744867543475873</v>
+        <v>-0.7504018131340523</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.5689549564970953</v>
+        <v>-0.7185048224495589</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.002141937360115366</v>
+        <v>-0.02174352416958084</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.528028519542327</v>
+        <v>-0.5593853470741559</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.03052410115034751</v>
+        <v>-0.4214809637465622</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>65.45837054279684</v>
+        <v>53.00200873054291</v>
       </c>
       <c r="B46" t="n">
-        <v>106.9111674102627</v>
+        <v>120.5958724481185</v>
       </c>
       <c r="C46" t="n">
-        <v>40.70467338436301</v>
+        <v>45.92057811178104</v>
       </c>
       <c r="D46" t="n">
-        <v>9.427200876654561</v>
+        <v>9.602648223093778</v>
       </c>
       <c r="E46" t="n">
-        <v>3.844034633493088</v>
+        <v>4.650827963548121</v>
       </c>
       <c r="F46" t="n">
-        <v>5.566754028180167</v>
+        <v>4.235073778590845</v>
       </c>
       <c r="G46" t="n">
-        <v>0.03909174442356719</v>
+        <v>0.08266142238650173</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8408137397395391</v>
+        <v>-0.6629921221448584</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8868021722816949</v>
+        <v>-0.7914404664624206</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9218770417405545</v>
+        <v>-0.7890772462241071</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.1000492003576648</v>
+        <v>-0.02113589557549721</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.3639785923629664</v>
+        <v>-0.2526393122051183</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.07238201609195122</v>
+        <v>-0.0675607112642379</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>56.74671976589561</v>
+        <v>39.64022399689333</v>
       </c>
       <c r="B47" t="n">
-        <v>123.4945002807638</v>
+        <v>115.1831851537375</v>
       </c>
       <c r="C47" t="n">
-        <v>41.06005562095125</v>
+        <v>45.68114478395836</v>
       </c>
       <c r="D47" t="n">
-        <v>9.989007457647428</v>
+        <v>6.996869688087682</v>
       </c>
       <c r="E47" t="n">
-        <v>3.290726652464553</v>
+        <v>4.540469195881045</v>
       </c>
       <c r="F47" t="n">
-        <v>4.672078874034444</v>
+        <v>3.125263389232218</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06591512583807503</v>
+        <v>0.2275081032881004</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7585819780017178</v>
+        <v>-0.2197769776169405</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8403444502651052</v>
+        <v>-0.5853268986230998</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8642994745344702</v>
+        <v>-0.3600139426714101</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.07887568356136918</v>
+        <v>-0.03067687994641386</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.2989019535966251</v>
+        <v>-0.5010547519803243</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.08465776660943111</v>
+        <v>-0.01283309347619679</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>72.60985294560236</v>
+        <v>90.41587964513334</v>
       </c>
       <c r="B48" t="n">
-        <v>114.390001952247</v>
+        <v>122.364907835012</v>
       </c>
       <c r="C48" t="n">
-        <v>38.96360917123794</v>
+        <v>46.19117080710733</v>
       </c>
       <c r="D48" t="n">
-        <v>8.580364257795154</v>
+        <v>6.80652396649585</v>
       </c>
       <c r="E48" t="n">
-        <v>3.527006299973762</v>
+        <v>3.163890752815393</v>
       </c>
       <c r="F48" t="n">
-        <v>6.353390168805323</v>
+        <v>8.836630195047901</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02695300656180204</v>
+        <v>0.01252721549138288</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8820874944367371</v>
+        <v>-0.9280807573475256</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9123683364535604</v>
+        <v>-0.9434664438797346</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9475002426396913</v>
+        <v>-0.9727121683254615</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.01352082693428029</v>
+        <v>-0.0541989114206237</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.4174006645843652</v>
+        <v>-0.519213142471575</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.05900818515844596</v>
+        <v>-0.129410470195961</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>68.8634659967375</v>
+        <v>99.99999997508768</v>
       </c>
       <c r="B49" t="n">
-        <v>104.8831532516528</v>
+        <v>116.0460748559863</v>
       </c>
       <c r="C49" t="n">
-        <v>40.76589940898504</v>
+        <v>45.88716767485425</v>
       </c>
       <c r="D49" t="n">
-        <v>8.654931350770356</v>
+        <v>5.684205555899331</v>
       </c>
       <c r="E49" t="n">
-        <v>3.4903149066093</v>
+        <v>4.628970721120143</v>
       </c>
       <c r="F49" t="n">
-        <v>5.864071210347564</v>
+        <v>10.36377349246432</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0324443874038875</v>
+        <v>0.009043526109255073</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8627106828999859</v>
+        <v>-0.9457551987092938</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9001927935369309</v>
+        <v>-0.9564615448356742</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.935799671836624</v>
+        <v>-0.9811837046864035</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.0004132759867443297</v>
+        <v>-1.59825232503526e-05</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.3894148928410061</v>
+        <v>-0.5874999998224997</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.07473801181768178</v>
+        <v>-0.05992403996668477</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>89.12938733043541</v>
+        <v>95.31669805214003</v>
       </c>
       <c r="B50" t="n">
-        <v>89.82215936622831</v>
+        <v>122.7493102482823</v>
       </c>
       <c r="C50" t="n">
-        <v>40.75998423541566</v>
+        <v>46.35250919155443</v>
       </c>
       <c r="D50" t="n">
-        <v>7.56967354607027</v>
+        <v>7.006123667844</v>
       </c>
       <c r="E50" t="n">
-        <v>3.514007499482859</v>
+        <v>4.296132884098071</v>
       </c>
       <c r="F50" t="n">
-        <v>8.680442934754895</v>
+        <v>9.73177308768615</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01341104451765984</v>
+        <v>0.01058485092736355</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.9341134263131055</v>
+        <v>-0.9379188734472254</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9477735291128326</v>
+        <v>-0.9505594726933443</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.975654521963889</v>
+        <v>-0.9775170084727156</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.2070200451746279</v>
+        <v>-0.2317652455499385</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.5408027383452154</v>
+        <v>-0.5541314736214976</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.07453853593047675</v>
+        <v>-0.1662878152124402</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>39.4232037181519</v>
+        <v>93.6015946864925</v>
       </c>
       <c r="B51" t="n">
-        <v>115.5471718126216</v>
+        <v>92.67622953028339</v>
       </c>
       <c r="C51" t="n">
-        <v>40.47104573460037</v>
+        <v>45.88716767485425</v>
       </c>
       <c r="D51" t="n">
-        <v>7.283679244916247</v>
+        <v>7.015232951729384</v>
       </c>
       <c r="E51" t="n">
-        <v>3.468678690895862</v>
+        <v>4.153500150478716</v>
       </c>
       <c r="F51" t="n">
-        <v>3.139835744750231</v>
+        <v>9.416164642835522</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2379017961306386</v>
+        <v>0.01121403975022971</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3076320370787783</v>
+        <v>-0.9347026073688472</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6234445392018982</v>
+        <v>-0.9482160576467838</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.4532134754860785</v>
+        <v>-0.9759711765924437</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.03051694569434645</v>
+        <v>-0.1832339013199222</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5117725162242122</v>
+        <v>-0.541911362141259</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.05926699058121541</v>
+        <v>-0.05992403996668477</v>
       </c>
     </row>
   </sheetData>
